--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486453_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486453_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5835</v>
+        <v>11.803</v>
       </c>
       <c r="E2" t="n">
-        <v>10.2242</v>
+        <v>9.888999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3592</v>
+        <v>1.9141</v>
       </c>
       <c r="G2" t="n">
         <v>11.9563</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0394</v>
+        <v>0.259</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1971</v>
+        <v>-0.1382</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1577</v>
+        <v>0.3972</v>
       </c>
       <c r="V2" t="n">
         <v>-1.4997</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2479</v>
+        <v>5.3375</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9272</v>
+        <v>4.8586</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3207</v>
+        <v>0.4789</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1545</v>
+        <v>5.9435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2644</v>
+        <v>0.6994</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8902</v>
+        <v>5.2441</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9268</v>
+        <v>7.1701</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9307</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9961</v>
+        <v>6.2179</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2277</v>
+        <v>-1.2266</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6663</v>
+        <v>-0.2528</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8941</v>
+        <v>-0.9738</v>
       </c>
       <c r="P3" t="n">
-        <v>1.305</v>
+        <v>-0.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1494</v>
+        <v>0.0688</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8051</v>
+        <v>-0.3317</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3442</v>
+        <v>0.4004</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6389</v>
+        <v>0.1952</v>
       </c>
       <c r="W3" t="n">
         <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0561</v>
+        <v>5.1458</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2998</v>
+        <v>2.2566</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7563</v>
+        <v>2.8892</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9435</v>
+        <v>2.1545</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6994</v>
+        <v>0.2644</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2441</v>
+        <v>1.8902</v>
       </c>
       <c r="J4" t="n">
-        <v>7.1701</v>
+        <v>1.9268</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9307</v>
       </c>
       <c r="L4" t="n">
-        <v>6.2179</v>
+        <v>0.9961</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2266</v>
+        <v>0.2277</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2528</v>
+        <v>-0.6663</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9738</v>
+        <v>0.8941</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2126</v>
+        <v>1.0473</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8904</v>
+        <v>0.1346</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.9127</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1952</v>
+        <v>0.6389</v>
       </c>
       <c r="W4" t="n">
         <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.4437</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6344</v>
+        <v>5.0351</v>
       </c>
       <c r="E5" t="n">
         <v>2.6485</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9859</v>
+        <v>2.3866</v>
       </c>
       <c r="G5" t="n">
         <v>5.2078</v>
@@ -844,13 +844,13 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2123</v>
+        <v>0.1884</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1454</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0669</v>
+        <v>0.3338</v>
       </c>
       <c r="V5" t="n">
         <v>0.074</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9274</v>
+        <v>3.3649</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7952</v>
+        <v>1.5717</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1322</v>
+        <v>1.7931</v>
       </c>
       <c r="G6" t="n">
         <v>2.3453</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6474</v>
+        <v>1.0848</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1971</v>
+        <v>-0.0264</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4503</v>
+        <v>1.1113</v>
       </c>
       <c r="V6" t="n">
         <v>0.3698</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9468</v>
+        <v>2.8639</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2861</v>
+        <v>2.9566</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3393</v>
+        <v>-0.0927</v>
       </c>
       <c r="G7" t="n">
         <v>1.541</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0157</v>
+        <v>-0.0985</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.1514</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1937</v>
+        <v>0.0529</v>
       </c>
       <c r="V7" t="n">
         <v>1.2039</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2226</v>
+        <v>1.4088</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1019</v>
+        <v>-1.4657</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8793</v>
+        <v>2.8746</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3225</v>
+        <v>0.5317</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0978</v>
+        <v>-0.6054</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7753</v>
+        <v>1.1371</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4148</v>
+        <v>-0.308</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.465</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8797</v>
+        <v>0.3275</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7372</v>
+        <v>0.8398</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6328</v>
+        <v>0.0302</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1044</v>
+        <v>0.8096</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2178</v>
+        <v>0.2376</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6872</v>
+        <v>-0.4182</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4694</v>
+        <v>0.6558</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7602</v>
+        <v>-0.6656</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7602</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7962</v>
+        <v>0.0171</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.801</v>
+        <v>-0.1284</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5972</v>
+        <v>0.1455</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5317</v>
+        <v>-0.1374</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6054</v>
+        <v>1.8157</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1371</v>
+        <v>-1.9531</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.308</v>
+        <v>1.1538</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6356000000000001</v>
+        <v>2.0685</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3275</v>
+        <v>-0.9147999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8398</v>
+        <v>-1.2911</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0302</v>
+        <v>-0.2528</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8096</v>
+        <v>-1.0383</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.375</v>
+        <v>0.1544</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3784</v>
+        <v>0.3491</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6656</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0131</v>
+        <v>0.0048</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6872</v>
+        <v>0.7609</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7003</v>
+        <v>-0.756</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1374</v>
+        <v>-0.3225</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8157</v>
+        <v>-1.0978</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9531</v>
+        <v>0.7753</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1538</v>
+        <v>0.4148</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0685</v>
+        <v>-0.465</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9147999999999999</v>
+        <v>0.8797</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2911</v>
+        <v>-0.7372</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2528</v>
+        <v>-0.6328</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0383</v>
+        <v>-0.1044</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1504</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.3461</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9039</v>
+        <v>-0.3461</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="11">
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0295</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.882</v>
+        <v>-0.7703</v>
       </c>
       <c r="F11" t="n">
         <v>-0.1475</v>
@@ -1312,10 +1312,10 @@
         <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1512</v>
+        <v>-2.9778</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9179</v>
+        <v>-2.8061</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2333</v>
+        <v>-0.1716</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8187</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4624</v>
+        <v>-0.289</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0856</v>
+        <v>0.1472</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6797</v>
+        <v>-3.5178</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9504</v>
+        <v>-2.7269</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.7909</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8838</v>
@@ -1468,13 +1468,13 @@
         <v>0.6525</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1096</v>
+        <v>0.0523</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3014</v>
+        <v>0.2397</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2512</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.56760000000001</v>
+        <v>27.56750000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>17.0444</v>
+        <v>17.0445</v>
       </c>
       <c r="F14" t="n">
-        <v>10.5231</v>
+        <v>10.5233</v>
       </c>
       <c r="G14" t="n">
-        <v>24.4077</v>
+        <v>24.40769999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>7.617899999999999</v>
+        <v>7.617900000000001</v>
       </c>
       <c r="I14" t="n">
         <v>16.7898</v>
@@ -1537,7 +1537,7 @@
         <v>-1.1437</v>
       </c>
       <c r="P14" t="n">
-        <v>2.175</v>
+        <v>2.174999999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-9.787700000000001</v>
@@ -1546,10 +1546,10 @@
         <v>11.9626</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6798</v>
+        <v>2.6799</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5743</v>
+        <v>-1.5742</v>
       </c>
       <c r="U14" t="n">
         <v>4.254</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0343</v>
+        <v>0.9727</v>
       </c>
       <c r="E15" t="n">
         <v>0.8334</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2009</v>
+        <v>0.1393</v>
       </c>
       <c r="G15" t="n">
         <v>0.8014</v>
@@ -1624,13 +1624,13 @@
         <v>0.2175</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0154</v>
+        <v>-0.0463</v>
       </c>
       <c r="T15" t="n">
         <v>-0.137</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1524</v>
+        <v>0.0907</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7184</v>
+        <v>0.8109</v>
       </c>
       <c r="E16" t="n">
         <v>0.7572</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0388</v>
+        <v>0.0537</v>
       </c>
       <c r="G16" t="n">
         <v>0.7252999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2244</v>
+        <v>-0.1319</v>
       </c>
       <c r="T16" t="n">
         <v>-0.137</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6516999999999999</v>
+        <v>-0.489</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8103</v>
+        <v>0.9162</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1586</v>
+        <v>-1.4052</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2749</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2332</v>
+        <v>0.0925</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7282</v>
+        <v>-0.1658</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5049</v>
+        <v>0.2584</v>
       </c>
       <c r="V17" t="n">
         <v>1.3459</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7423</v>
+        <v>-1.6521</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0077</v>
+        <v>0.2573</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7346</v>
+        <v>-1.9094</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.9698</v>
+        <v>-0.0209</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.211</v>
+        <v>-1.0799</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.7588</v>
+        <v>1.059</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3416</v>
+        <v>3.1317</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8331</v>
+        <v>-0.1976</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5084</v>
+        <v>3.3293</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.6283</v>
+        <v>-3.1526</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3779</v>
+        <v>-0.8823</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2504</v>
+        <v>-2.2703</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0875</v>
+        <v>-0.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1405</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5564</v>
+        <v>-0.6994</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6969</v>
+        <v>0.1334</v>
       </c>
       <c r="V18" t="n">
-        <v>2.9995</v>
+        <v>-0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1093</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3227</v>
+        <v>-1.7907</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4133</v>
+        <v>0.9725</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9094</v>
+        <v>-2.7632</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0209</v>
+        <v>0.4925</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0799</v>
+        <v>3.601</v>
       </c>
       <c r="I19" t="n">
-        <v>1.059</v>
+        <v>-3.1085</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1317</v>
+        <v>4.3105</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1976</v>
+        <v>4.7662</v>
       </c>
       <c r="L19" t="n">
-        <v>3.3293</v>
+        <v>-0.4558</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1526</v>
+        <v>-3.818</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8823</v>
+        <v>-1.1652</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2703</v>
+        <v>-2.6528</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2365</v>
+        <v>-0.8259</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3699</v>
+        <v>-0.7931</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1334</v>
+        <v>-0.0328</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9737</v>
+        <v>-2.1931</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1902</v>
+        <v>-1.1195</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1639</v>
+        <v>-1.0736</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4925</v>
+        <v>-5.9698</v>
       </c>
       <c r="H20" t="n">
-        <v>3.601</v>
+        <v>-2.211</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.1085</v>
+        <v>-3.7588</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3105</v>
+        <v>-2.3416</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7662</v>
+        <v>-0.8331</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4558</v>
+        <v>-1.5084</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.818</v>
+        <v>-3.6283</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1652</v>
+        <v>-1.3779</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.6528</v>
+        <v>-2.2504</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0875</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0089</v>
+        <v>-0.3103</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5754</v>
+        <v>-0.6681</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4335</v>
+        <v>0.3578</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3698</v>
+        <v>2.9995</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3698</v>
+        <v>1.8902</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.1093</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. DE BISSCHOP</t>
+          <t>P. RIGOT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6712</v>
+        <v>-5.3835</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1409</v>
+        <v>-4.4584</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5303</v>
+        <v>-0.9252</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.2846</v>
+        <v>-4.1752</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.7649</v>
+        <v>-1.5177</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5196</v>
+        <v>-2.6575</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6428</v>
+        <v>-2.1439</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7575</v>
+        <v>-0.6538</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1147</v>
+        <v>-1.4901</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.6418</v>
+        <v>-2.0313</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0074</v>
+        <v>-0.8639</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6344</v>
+        <v>-1.1674</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1784</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3942</v>
+        <v>-0.1394</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7842</v>
+        <v>0.0616</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.1745</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7602</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. RIGOT</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9288</v>
+        <v>-5.8811</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7878</v>
+        <v>-1.6429</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1409</v>
+        <v>-4.2382</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.1752</v>
+        <v>-2.468</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5177</v>
+        <v>-2.3692</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.6575</v>
+        <v>-0.0988</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1439</v>
+        <v>1.695</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6538</v>
+        <v>-0.392</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4901</v>
+        <v>2.087</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0313</v>
+        <v>-4.1631</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8639</v>
+        <v>-1.9773</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1674</v>
+        <v>-2.1858</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.377</v>
+        <v>-0.6306</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5312</v>
+        <v>-0.7931</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1542</v>
+        <v>0.1625</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1745</v>
+        <v>-1.695</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1745</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>B. DE BISSCHOP</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.331</v>
+        <v>-5.885</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3393</v>
+        <v>-2.9232</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9916</v>
+        <v>-2.9618</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.2336</v>
+        <v>-5.2846</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.5975</v>
+        <v>-3.7649</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6361</v>
+        <v>-1.5196</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.783</v>
+        <v>-1.6428</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.7152</v>
+        <v>-1.7575</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.0678</v>
+        <v>0.1147</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.4506</v>
+        <v>-3.6418</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8823</v>
+        <v>-2.0074</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5683</v>
+        <v>-1.6344</v>
       </c>
       <c r="P23" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4024</v>
+        <v>-0.0354</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5564</v>
+        <v>-0.3881</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1539</v>
+        <v>0.3527</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0025</v>
+        <v>-6.0766</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4252</v>
+        <v>-4.1158</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.5773</v>
+        <v>-1.9608</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.468</v>
+        <v>-7.2336</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3692</v>
+        <v>-3.5975</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0988</v>
+        <v>-3.6361</v>
       </c>
       <c r="J24" t="n">
-        <v>1.695</v>
+        <v>-3.783</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.392</v>
+        <v>-2.7152</v>
       </c>
       <c r="L24" t="n">
-        <v>2.087</v>
+        <v>-1.0678</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.1631</v>
+        <v>-3.4506</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.9773</v>
+        <v>-0.8823</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1858</v>
+        <v>-2.5683</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.7519</v>
+        <v>-0.1481</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5754</v>
+        <v>-0.3329</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1765</v>
+        <v>0.1847</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-27.5678</v>
+        <v>-27.5675</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.5231</v>
+        <v>-10.5232</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.0445</v>
+        <v>-17.0444</v>
       </c>
       <c r="G25" t="n">
         <v>-24.4078</v>
@@ -2380,7 +2380,7 @@
         <v>3.0017</v>
       </c>
       <c r="K25" t="n">
-        <v>1.858099999999999</v>
+        <v>1.858100000000001</v>
       </c>
       <c r="L25" t="n">
         <v>1.1435</v>
@@ -2404,7 +2404,7 @@
         <v>9.7875</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.6796</v>
+        <v>-2.6798</v>
       </c>
       <c r="T25" t="n">
         <v>-4.2539</v>
@@ -2419,7 +2419,7 @@
         <v>2.6917</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.9968</v>
+        <v>-0.9968000000000001</v>
       </c>
     </row>
   </sheetData>
